--- a/Team-Data/2013-14/4-5-2013-14.xlsx
+++ b/Team-Data/2013-14/4-5-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -751,7 +818,7 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI2" t="n">
         <v>18</v>
@@ -772,7 +839,7 @@
         <v>12</v>
       </c>
       <c r="AO2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP2" t="n">
         <v>22</v>
@@ -805,7 +872,7 @@
         <v>12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
         <v>21</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E3" t="n">
         <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3" t="n">
-        <v>0.299</v>
+        <v>0.303</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
@@ -861,25 +928,25 @@
         <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K3" t="n">
-        <v>0.433</v>
+        <v>0.432</v>
       </c>
       <c r="L3" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M3" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.328</v>
+        <v>0.326</v>
       </c>
       <c r="O3" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P3" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
         <v>0.775</v>
@@ -888,7 +955,7 @@
         <v>12.1</v>
       </c>
       <c r="S3" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T3" t="n">
         <v>42.7</v>
@@ -897,13 +964,13 @@
         <v>20.8</v>
       </c>
       <c r="V3" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W3" t="n">
         <v>7.1</v>
       </c>
       <c r="X3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y3" t="n">
         <v>4.6</v>
@@ -915,13 +982,13 @@
         <v>19.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="AC3" t="n">
         <v>-4.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE3" t="n">
         <v>27</v>
@@ -933,7 +1000,7 @@
         <v>27</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
         <v>24</v>
@@ -945,7 +1012,7 @@
         <v>28</v>
       </c>
       <c r="AL3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AM3" t="n">
         <v>19</v>
@@ -957,7 +1024,7 @@
         <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
@@ -993,7 +1060,7 @@
         <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC3" t="n">
         <v>25</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F4" t="n">
         <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>0.553</v>
+        <v>0.547</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J4" t="n">
         <v>78.09999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L4" t="n">
         <v>8.6</v>
@@ -1055,7 +1122,7 @@
         <v>23.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O4" t="n">
         <v>18.5</v>
@@ -1070,13 +1137,13 @@
         <v>8.699999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T4" t="n">
         <v>38.1</v>
       </c>
       <c r="U4" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V4" t="n">
         <v>14.3</v>
@@ -1088,7 +1155,7 @@
         <v>3.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z4" t="n">
         <v>21.9</v>
@@ -1103,7 +1170,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
         <v>14</v>
@@ -1115,16 +1182,16 @@
         <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ4" t="n">
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1133,7 +1200,7 @@
         <v>10</v>
       </c>
       <c r="AN4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO4" t="n">
         <v>10</v>
@@ -1148,16 +1215,16 @@
         <v>29</v>
       </c>
       <c r="AS4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT4" t="n">
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
         <v>6</v>
@@ -1172,7 +1239,7 @@
         <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>20</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -1207,55 +1274,55 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="n">
         <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>0.506</v>
+        <v>0.5</v>
       </c>
       <c r="H5" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J5" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L5" t="n">
         <v>6.2</v>
       </c>
       <c r="M5" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="N5" t="n">
         <v>0.352</v>
       </c>
       <c r="O5" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P5" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.741</v>
+        <v>0.742</v>
       </c>
       <c r="R5" t="n">
         <v>9.4</v>
       </c>
       <c r="S5" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="T5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="U5" t="n">
         <v>21.4</v>
@@ -1264,55 +1331,55 @@
         <v>12.3</v>
       </c>
       <c r="W5" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="X5" t="n">
         <v>5.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z5" t="n">
         <v>18.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
         <v>96.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
       </c>
       <c r="AF5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
         <v>25</v>
       </c>
       <c r="AM5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN5" t="n">
         <v>18</v>
@@ -1330,13 +1397,13 @@
         <v>25</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1354,7 +1421,7 @@
         <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB5" t="n">
         <v>24</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>0.584</v>
+        <v>0.579</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
@@ -1410,13 +1477,13 @@
         <v>80.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L6" t="n">
         <v>6.1</v>
       </c>
       <c r="M6" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="N6" t="n">
         <v>0.347</v>
@@ -1452,25 +1519,25 @@
         <v>5.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z6" t="n">
         <v>19.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF6" t="n">
         <v>12</v>
@@ -1479,7 +1546,7 @@
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI6" t="n">
         <v>30</v>
@@ -1494,7 +1561,7 @@
         <v>27</v>
       </c>
       <c r="AM6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN6" t="n">
         <v>25</v>
@@ -1503,10 +1570,10 @@
         <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
         <v>10</v>
@@ -1521,19 +1588,19 @@
         <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW6" t="n">
         <v>21</v>
       </c>
       <c r="AX6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>28</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA6" t="n">
         <v>9</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -1571,28 +1638,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E7" t="n">
         <v>31</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>0.397</v>
+        <v>0.403</v>
       </c>
       <c r="H7" t="n">
         <v>48.6</v>
       </c>
       <c r="I7" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J7" t="n">
-        <v>84.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0.433</v>
+        <v>0.434</v>
       </c>
       <c r="L7" t="n">
         <v>7.1</v>
@@ -1601,7 +1668,7 @@
         <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O7" t="n">
         <v>17.1</v>
@@ -1610,16 +1677,16 @@
         <v>22.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.752</v>
+        <v>0.751</v>
       </c>
       <c r="R7" t="n">
         <v>12</v>
       </c>
       <c r="S7" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U7" t="n">
         <v>20.8</v>
@@ -1628,7 +1695,7 @@
         <v>14.3</v>
       </c>
       <c r="W7" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X7" t="n">
         <v>3.7</v>
@@ -1661,13 +1728,13 @@
         <v>22</v>
       </c>
       <c r="AH7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI7" t="n">
         <v>22</v>
       </c>
       <c r="AJ7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK7" t="n">
         <v>27</v>
@@ -1694,16 +1761,16 @@
         <v>7</v>
       </c>
       <c r="AS7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT7" t="n">
         <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
         <v>25</v>
@@ -1718,7 +1785,7 @@
         <v>9</v>
       </c>
       <c r="BA7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB7" t="n">
         <v>22</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
@@ -2025,7 +2092,7 @@
         <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
         <v>12</v>
@@ -2034,10 +2101,10 @@
         <v>5</v>
       </c>
       <c r="AK9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
@@ -2058,7 +2125,7 @@
         <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
         <v>5</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F10" t="n">
         <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>0.364</v>
+        <v>0.355</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2135,28 +2202,28 @@
         <v>38.9</v>
       </c>
       <c r="J10" t="n">
-        <v>86.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="K10" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L10" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M10" t="n">
         <v>19.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.32</v>
+        <v>0.319</v>
       </c>
       <c r="O10" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="P10" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.671</v>
+        <v>0.668</v>
       </c>
       <c r="R10" t="n">
         <v>14.4</v>
@@ -2171,31 +2238,31 @@
         <v>21.1</v>
       </c>
       <c r="V10" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W10" t="n">
         <v>8.4</v>
       </c>
       <c r="X10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y10" t="n">
         <v>4.9</v>
       </c>
-      <c r="Y10" t="n">
-        <v>4.8</v>
-      </c>
       <c r="Z10" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>100.9</v>
+        <v>100.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.5</v>
+        <v>-3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,16 +2274,16 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ10" t="n">
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="n">
         <v>26</v>
@@ -2228,7 +2295,7 @@
         <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP10" t="n">
         <v>6</v>
@@ -2246,7 +2313,7 @@
         <v>3</v>
       </c>
       <c r="AU10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV10" t="n">
         <v>12</v>
@@ -2255,19 +2322,19 @@
         <v>7</v>
       </c>
       <c r="AX10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
         <v>17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,7 +2456,7 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
         <v>6</v>
@@ -2398,7 +2465,7 @@
         <v>7</v>
       </c>
       <c r="AK11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL11" t="n">
         <v>7</v>
@@ -2428,7 +2495,7 @@
         <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV11" t="n">
         <v>21</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>4.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
@@ -2610,7 +2677,7 @@
         <v>4</v>
       </c>
       <c r="AU12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2631,7 +2698,7 @@
         <v>1</v>
       </c>
       <c r="BB12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC12" t="n">
         <v>6</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>4.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>4</v>
@@ -2753,7 +2820,7 @@
         <v>5</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI13" t="n">
         <v>26</v>
@@ -2762,7 +2829,7 @@
         <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL13" t="n">
         <v>24</v>
@@ -2795,7 +2862,7 @@
         <v>28</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>27</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2962,13 +3029,13 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT14" t="n">
         <v>15</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3138,7 +3205,7 @@
         <v>4</v>
       </c>
       <c r="AO15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP15" t="n">
         <v>19</v>
@@ -3150,7 +3217,7 @@
         <v>26</v>
       </c>
       <c r="AS15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT15" t="n">
         <v>23</v>
@@ -3168,7 +3235,7 @@
         <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>1.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE16" t="n">
         <v>10</v>
@@ -3305,7 +3372,7 @@
         <v>15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
         <v>7</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
@@ -3359,7 +3426,7 @@
         <v>29</v>
       </c>
       <c r="BB16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC16" t="n">
         <v>14</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM17" t="n">
         <v>15</v>
@@ -3514,7 +3581,7 @@
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3523,7 +3590,7 @@
         <v>10</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
         <v>2</v>
@@ -3538,7 +3605,7 @@
         <v>8</v>
       </c>
       <c r="BA17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>11</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E18" t="n">
         <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G18" t="n">
-        <v>0.182</v>
+        <v>0.184</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3591,43 +3658,43 @@
         <v>35.8</v>
       </c>
       <c r="J18" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L18" t="n">
         <v>6.8</v>
       </c>
       <c r="M18" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="O18" t="n">
         <v>16.5</v>
       </c>
       <c r="P18" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.752</v>
+        <v>0.751</v>
       </c>
       <c r="R18" t="n">
         <v>11.9</v>
       </c>
       <c r="S18" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T18" t="n">
         <v>41.1</v>
       </c>
       <c r="U18" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V18" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W18" t="n">
         <v>6.7</v>
@@ -3642,16 +3709,16 @@
         <v>20.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>95</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3666,22 +3733,22 @@
         <v>8</v>
       </c>
       <c r="AI18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK18" t="n">
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AM18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
         <v>22</v>
@@ -3702,7 +3769,7 @@
         <v>24</v>
       </c>
       <c r="AU18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV18" t="n">
         <v>18</v>
@@ -3711,7 +3778,7 @@
         <v>28</v>
       </c>
       <c r="AX18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
         <v>21</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E19" t="n">
         <v>38</v>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.507</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
@@ -3773,19 +3840,19 @@
         <v>38.9</v>
       </c>
       <c r="J19" t="n">
-        <v>87.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L19" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M19" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.342</v>
+        <v>0.345</v>
       </c>
       <c r="O19" t="n">
         <v>21.5</v>
@@ -3794,16 +3861,16 @@
         <v>27.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.777</v>
+        <v>0.778</v>
       </c>
       <c r="R19" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S19" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T19" t="n">
-        <v>44.7</v>
+        <v>44.9</v>
       </c>
       <c r="U19" t="n">
         <v>23.9</v>
@@ -3812,7 +3879,7 @@
         <v>13.8</v>
       </c>
       <c r="W19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X19" t="n">
         <v>3.5</v>
@@ -3821,40 +3888,40 @@
         <v>5.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AA19" t="n">
         <v>23.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.7</v>
+        <v>106.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE19" t="n">
         <v>16</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>17</v>
       </c>
       <c r="AF19" t="n">
         <v>16</v>
       </c>
       <c r="AG19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL19" t="n">
         <v>17</v>
@@ -3872,13 +3939,13 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
         <v>8</v>
@@ -3905,10 +3972,10 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BC19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
         <v>21</v>
@@ -4045,7 +4112,7 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO20" t="n">
         <v>12</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>18</v>
@@ -4209,13 +4276,13 @@
         <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI21" t="n">
         <v>19</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK21" t="n">
         <v>14</v>
@@ -4266,7 +4333,7 @@
         <v>23</v>
       </c>
       <c r="BA21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4430,7 +4497,7 @@
         <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV22" t="n">
         <v>27</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F23" t="n">
         <v>55</v>
       </c>
       <c r="G23" t="n">
-        <v>0.286</v>
+        <v>0.276</v>
       </c>
       <c r="H23" t="n">
         <v>48.7</v>
@@ -4504,46 +4571,46 @@
         <v>83.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L23" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
       <c r="O23" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="P23" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="R23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T23" t="n">
         <v>42.4</v>
       </c>
       <c r="U23" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V23" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W23" t="n">
         <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y23" t="n">
         <v>5.6</v>
@@ -4552,16 +4619,16 @@
         <v>20.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.2</v>
+        <v>-5.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4576,7 +4643,7 @@
         <v>2</v>
       </c>
       <c r="AI23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ23" t="n">
         <v>13</v>
@@ -4591,10 +4658,10 @@
         <v>21</v>
       </c>
       <c r="AN23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AO23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP23" t="n">
         <v>27</v>
@@ -4609,25 +4676,25 @@
         <v>10</v>
       </c>
       <c r="AT23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU23" t="n">
         <v>22</v>
       </c>
       <c r="AV23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW23" t="n">
         <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY23" t="n">
         <v>24</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E24" t="n">
         <v>17</v>
       </c>
       <c r="F24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G24" t="n">
-        <v>0.221</v>
+        <v>0.224</v>
       </c>
       <c r="H24" t="n">
         <v>48.5</v>
@@ -4683,28 +4750,28 @@
         <v>37.7</v>
       </c>
       <c r="J24" t="n">
-        <v>87.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="K24" t="n">
         <v>0.431</v>
       </c>
       <c r="L24" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M24" t="n">
         <v>22.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0.312</v>
+        <v>0.31</v>
       </c>
       <c r="O24" t="n">
         <v>16.6</v>
       </c>
       <c r="P24" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.709</v>
+        <v>0.71</v>
       </c>
       <c r="R24" t="n">
         <v>11.8</v>
@@ -4719,7 +4786,7 @@
         <v>21.9</v>
       </c>
       <c r="V24" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="W24" t="n">
         <v>9.300000000000001</v>
@@ -4737,13 +4804,13 @@
         <v>20.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>99.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="AC24" t="n">
         <v>-10.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4755,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI24" t="n">
         <v>17</v>
@@ -4794,7 +4861,7 @@
         <v>14</v>
       </c>
       <c r="AU24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4812,7 +4879,7 @@
         <v>25</v>
       </c>
       <c r="BA24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB24" t="n">
         <v>19</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4961,7 +5028,7 @@
         <v>9</v>
       </c>
       <c r="AP25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ25" t="n">
         <v>16</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>3.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5149,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS26" t="n">
         <v>6</v>
@@ -5158,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="AU26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
@@ -5179,7 +5246,7 @@
         <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC26" t="n">
         <v>8</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -5289,31 +5356,31 @@
         <v>-2.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF27" t="n">
         <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM27" t="n">
         <v>26</v>
@@ -5334,7 +5401,7 @@
         <v>4</v>
       </c>
       <c r="AS27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT27" t="n">
         <v>9</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5495,7 +5562,7 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM28" t="n">
         <v>17</v>
@@ -5531,7 +5598,7 @@
         <v>19</v>
       </c>
       <c r="AX28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E29" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F29" t="n">
         <v>32</v>
       </c>
       <c r="G29" t="n">
-        <v>0.584</v>
+        <v>0.579</v>
       </c>
       <c r="H29" t="n">
         <v>48.7</v>
@@ -5599,13 +5666,13 @@
         <v>0.444</v>
       </c>
       <c r="L29" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M29" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="N29" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O29" t="n">
         <v>19.4</v>
@@ -5623,13 +5690,13 @@
         <v>31.2</v>
       </c>
       <c r="T29" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U29" t="n">
         <v>21.2</v>
       </c>
       <c r="V29" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W29" t="n">
         <v>7.1</v>
@@ -5653,10 +5720,10 @@
         <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF29" t="n">
         <v>12</v>
@@ -5674,10 +5741,10 @@
         <v>21</v>
       </c>
       <c r="AK29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM29" t="n">
         <v>11</v>
@@ -5689,7 +5756,7 @@
         <v>6</v>
       </c>
       <c r="AP29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ29" t="n">
         <v>6</v>
@@ -5725,10 +5792,10 @@
         <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-6.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
         <v>26</v>
@@ -5856,16 +5923,16 @@
         <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL30" t="n">
         <v>22</v>
       </c>
       <c r="AM30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO30" t="n">
         <v>23</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E31" t="n">
         <v>40</v>
       </c>
       <c r="F31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G31" t="n">
-        <v>0.519</v>
+        <v>0.526</v>
       </c>
       <c r="H31" t="n">
         <v>48.9</v>
@@ -5960,31 +6027,31 @@
         <v>84.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L31" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M31" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0.385</v>
+        <v>0.387</v>
       </c>
       <c r="O31" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="P31" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.732</v>
+        <v>0.734</v>
       </c>
       <c r="R31" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S31" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T31" t="n">
         <v>42.3</v>
@@ -6008,16 +6075,16 @@
         <v>20.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>100.4</v>
+        <v>100.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6032,16 +6099,16 @@
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK31" t="n">
         <v>12</v>
       </c>
       <c r="AL31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM31" t="n">
         <v>18</v>
@@ -6053,10 +6120,10 @@
         <v>28</v>
       </c>
       <c r="AP31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR31" t="n">
         <v>17</v>
@@ -6068,16 +6135,16 @@
         <v>20</v>
       </c>
       <c r="AU31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW31" t="n">
         <v>11</v>
       </c>
       <c r="AX31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6086,10 +6153,10 @@
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BC31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-5-2013-14</t>
+          <t>2014-04-05</t>
         </is>
       </c>
     </row>
